--- a/생활속의통계/Excel/7주차 실습데이터 1012_202204013변하연.xlsx
+++ b/생활속의통계/Excel/7주차 실습데이터 1012_202204013변하연.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KBS\Desktop\26_2_myLecture\생활속의통계\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KBS\Desktop\hayeun\26_2_myLecture\생활속의통계\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19BB8470-EC48-452A-9B46-600A7CA2C0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D819916A-EA3A-49D8-9720-D5C1709247C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="664" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="664" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="예제1" sheetId="33" r:id="rId1"/>
@@ -11251,10 +11251,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26B012CF-53E8-4BF2-B38C-E492CB909E30}">
   <dimension ref="A1:C69"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.8125" customWidth="1"/>
-    <col min="2" max="2" width="9.875" customWidth="1"/>
+    <col min="1" max="2" width="9.875" customWidth="1"/>
     <col min="3" max="3" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12112,10 +12111,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8884C42-8EB1-47E3-B196-0D22EFB5D35B}">
   <dimension ref="A1:C69"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.8125" customWidth="1"/>
-    <col min="2" max="2" width="9.875" customWidth="1"/>
+    <col min="1" max="2" width="9.875" customWidth="1"/>
     <col min="3" max="3" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12973,9 +12971,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46C8959D-42BE-4C33-B006-B70DEFEE15EA}">
   <dimension ref="A1:C69"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.8125" customWidth="1"/>
+    <col min="1" max="1" width="9.875" customWidth="1"/>
     <col min="2" max="2" width="9.875" style="8" customWidth="1"/>
     <col min="3" max="3" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
@@ -13834,9 +13832,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54FBAD2A-188E-496E-B224-EC7054F200A8}">
   <dimension ref="A1:C69"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.8125" customWidth="1"/>
+    <col min="1" max="1" width="9.875" customWidth="1"/>
     <col min="2" max="2" width="9.875" style="8" customWidth="1"/>
     <col min="3" max="3" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
@@ -14695,11 +14693,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57069260-7FA2-4E79-8314-04DDCED38F04}">
   <dimension ref="B1:F188"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="3" width="10.6875" customWidth="1"/>
+    <col min="2" max="3" width="10.75" customWidth="1"/>
     <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.6875" customWidth="1"/>
+    <col min="5" max="6" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -16118,11 +16116,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F54BF6C-12E6-467C-B219-053BF86DC626}">
   <dimension ref="B1:D188"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="3" width="10.6875" customWidth="1"/>
+    <col min="2" max="3" width="10.75" customWidth="1"/>
     <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.6875" customWidth="1"/>
+    <col min="5" max="6" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4">
@@ -17537,9 +17535,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AF8835E-3423-4D01-B146-9D4B0DEBBD61}">
   <dimension ref="B1:D148"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="3" width="10.6875" customWidth="1"/>
+    <col min="2" max="3" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4">
@@ -18433,9 +18431,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7CFA6C7-FD8D-4481-9A31-0E3B8FEC072D}">
   <dimension ref="B1:D148"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="3" width="10.6875" customWidth="1"/>
+    <col min="2" max="3" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4">
